--- a/week-01/digital_storytelling_sales_dataset.xlsx
+++ b/week-01/digital_storytelling_sales_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Student\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0B23594-2816-4494-99B4-4FA88059C18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D93C29F-23F7-4472-9D49-E90675DBD057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Retail Sales Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="15" r:id="rId2"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="121">
   <si>
     <t>Order ID</t>
   </si>
@@ -390,6 +415,15 @@
   </si>
   <si>
     <t>2025-02-08</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Total Sales</t>
   </si>
 </sst>
 </file>
@@ -425,8 +459,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,6 +481,1502 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Student" refreshedDate="46126.40730648148" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="120" xr:uid="{1BB941E7-D0F9-4E8D-A1B3-3563DEB1443A}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:I121" sheet="Retail Sales Data"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Order ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1001" maxValue="1120"/>
+    </cacheField>
+    <cacheField name="Date" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="South"/>
+        <s v="East"/>
+        <s v="West"/>
+        <s v="North"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="8">
+        <s v="Laptop"/>
+        <s v="Monitor"/>
+        <s v="Desk"/>
+        <s v="Printer"/>
+        <s v="Bookshelf"/>
+        <s v="Chair"/>
+        <s v="Phone"/>
+        <s v="Tablet"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Customer" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Units Sold" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="8"/>
+    </cacheField>
+    <cacheField name="Unit Price" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="120" maxValue="900"/>
+    </cacheField>
+    <cacheField name="Total Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="120" maxValue="7200"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="120">
+  <r>
+    <n v="1001"/>
+    <s v="2025-04-21"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Hernandez"/>
+    <n v="2"/>
+    <n v="900"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <n v="1002"/>
+    <s v="2025-03-21"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Lopez"/>
+    <n v="8"/>
+    <n v="300"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <n v="1003"/>
+    <s v="2025-01-18"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Wilson"/>
+    <n v="6"/>
+    <n v="350"/>
+    <n v="2100"/>
+  </r>
+  <r>
+    <n v="1004"/>
+    <s v="2025-04-28"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Taylor"/>
+    <n v="2"/>
+    <n v="350"/>
+    <n v="700"/>
+  </r>
+  <r>
+    <n v="1005"/>
+    <s v="2025-03-19"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Anderson"/>
+    <n v="5"/>
+    <n v="250"/>
+    <n v="1250"/>
+  </r>
+  <r>
+    <n v="1006"/>
+    <s v="2025-04-19"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Wilson"/>
+    <n v="1"/>
+    <n v="200"/>
+    <n v="200"/>
+  </r>
+  <r>
+    <n v="1007"/>
+    <s v="2025-02-03"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Smith"/>
+    <n v="7"/>
+    <n v="200"/>
+    <n v="1400"/>
+  </r>
+  <r>
+    <n v="1008"/>
+    <s v="2025-04-02"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Taylor"/>
+    <n v="5"/>
+    <n v="200"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <n v="1009"/>
+    <s v="2025-02-10"/>
+    <x v="2"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Anderson"/>
+    <n v="5"/>
+    <n v="120"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1010"/>
+    <s v="2025-02-25"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Lopez"/>
+    <n v="7"/>
+    <n v="300"/>
+    <n v="2100"/>
+  </r>
+  <r>
+    <n v="1011"/>
+    <s v="2025-03-17"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Rodriguez"/>
+    <n v="1"/>
+    <n v="900"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <n v="1012"/>
+    <s v="2025-03-30"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Davis"/>
+    <n v="7"/>
+    <n v="900"/>
+    <n v="6300"/>
+  </r>
+  <r>
+    <n v="1013"/>
+    <s v="2025-04-08"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Thomas"/>
+    <n v="7"/>
+    <n v="900"/>
+    <n v="6300"/>
+  </r>
+  <r>
+    <n v="1014"/>
+    <s v="2025-03-22"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Jones"/>
+    <n v="6"/>
+    <n v="200"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1015"/>
+    <s v="2025-03-25"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Taylor"/>
+    <n v="7"/>
+    <n v="300"/>
+    <n v="2100"/>
+  </r>
+  <r>
+    <n v="1016"/>
+    <s v="2025-03-19"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Brown"/>
+    <n v="5"/>
+    <n v="900"/>
+    <n v="4500"/>
+  </r>
+  <r>
+    <n v="1017"/>
+    <s v="2025-03-24"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Jackson"/>
+    <n v="2"/>
+    <n v="600"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1018"/>
+    <s v="2025-03-15"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Taylor"/>
+    <n v="4"/>
+    <n v="600"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <n v="1019"/>
+    <s v="2025-04-27"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Taylor"/>
+    <n v="3"/>
+    <n v="300"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <n v="1020"/>
+    <s v="2025-03-22"/>
+    <x v="1"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Rodriguez"/>
+    <n v="2"/>
+    <n v="600"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1021"/>
+    <s v="2025-01-07"/>
+    <x v="2"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Garcia"/>
+    <n v="3"/>
+    <n v="120"/>
+    <n v="360"/>
+  </r>
+  <r>
+    <n v="1022"/>
+    <s v="2025-02-06"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Lopez"/>
+    <n v="7"/>
+    <n v="200"/>
+    <n v="1400"/>
+  </r>
+  <r>
+    <n v="1023"/>
+    <s v="2025-04-04"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Smith"/>
+    <n v="8"/>
+    <n v="350"/>
+    <n v="2800"/>
+  </r>
+  <r>
+    <n v="1024"/>
+    <s v="2025-04-04"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Johnson"/>
+    <n v="4"/>
+    <n v="250"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <n v="1025"/>
+    <s v="2025-03-25"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Johnson"/>
+    <n v="7"/>
+    <n v="600"/>
+    <n v="4200"/>
+  </r>
+  <r>
+    <n v="1026"/>
+    <s v="2025-02-05"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Davis"/>
+    <n v="3"/>
+    <n v="200"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1027"/>
+    <s v="2025-03-16"/>
+    <x v="1"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Johnson"/>
+    <n v="7"/>
+    <n v="400"/>
+    <n v="2800"/>
+  </r>
+  <r>
+    <n v="1028"/>
+    <s v="2025-04-01"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Davis"/>
+    <n v="2"/>
+    <n v="120"/>
+    <n v="240"/>
+  </r>
+  <r>
+    <n v="1029"/>
+    <s v="2025-01-08"/>
+    <x v="0"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Thomas"/>
+    <n v="7"/>
+    <n v="400"/>
+    <n v="2800"/>
+  </r>
+  <r>
+    <n v="1030"/>
+    <s v="2025-03-03"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Smith"/>
+    <n v="8"/>
+    <n v="250"/>
+    <n v="2000"/>
+  </r>
+  <r>
+    <n v="1031"/>
+    <s v="2025-01-27"/>
+    <x v="1"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Williams"/>
+    <n v="3"/>
+    <n v="300"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <n v="1032"/>
+    <s v="2025-03-06"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Garcia"/>
+    <n v="6"/>
+    <n v="200"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1033"/>
+    <s v="2025-01-19"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Miller"/>
+    <n v="2"/>
+    <n v="200"/>
+    <n v="400"/>
+  </r>
+  <r>
+    <n v="1034"/>
+    <s v="2025-03-14"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Taylor"/>
+    <n v="6"/>
+    <n v="900"/>
+    <n v="5400"/>
+  </r>
+  <r>
+    <n v="1035"/>
+    <s v="2025-01-13"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Thomas"/>
+    <n v="6"/>
+    <n v="900"/>
+    <n v="5400"/>
+  </r>
+  <r>
+    <n v="1036"/>
+    <s v="2025-02-01"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Johnson"/>
+    <n v="8"/>
+    <n v="250"/>
+    <n v="2000"/>
+  </r>
+  <r>
+    <n v="1037"/>
+    <s v="2025-04-17"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Smith"/>
+    <n v="3"/>
+    <n v="250"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <n v="1038"/>
+    <s v="2025-03-15"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Martinez"/>
+    <n v="2"/>
+    <n v="300"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1039"/>
+    <s v="2025-03-14"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Miller"/>
+    <n v="8"/>
+    <n v="350"/>
+    <n v="2800"/>
+  </r>
+  <r>
+    <n v="1040"/>
+    <s v="2025-01-24"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Smith"/>
+    <n v="2"/>
+    <n v="250"/>
+    <n v="500"/>
+  </r>
+  <r>
+    <n v="1041"/>
+    <s v="2025-01-21"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Martin"/>
+    <n v="7"/>
+    <n v="600"/>
+    <n v="4200"/>
+  </r>
+  <r>
+    <n v="1042"/>
+    <s v="2025-03-19"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Taylor"/>
+    <n v="5"/>
+    <n v="250"/>
+    <n v="1250"/>
+  </r>
+  <r>
+    <n v="1043"/>
+    <s v="2025-03-30"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Martinez"/>
+    <n v="3"/>
+    <n v="250"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <n v="1044"/>
+    <s v="2025-02-26"/>
+    <x v="3"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Lopez"/>
+    <n v="2"/>
+    <n v="400"/>
+    <n v="800"/>
+  </r>
+  <r>
+    <n v="1045"/>
+    <s v="2025-01-13"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Thomas"/>
+    <n v="1"/>
+    <n v="900"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <n v="1046"/>
+    <s v="2025-01-30"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Gonzalez"/>
+    <n v="6"/>
+    <n v="900"/>
+    <n v="5400"/>
+  </r>
+  <r>
+    <n v="1047"/>
+    <s v="2025-02-19"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Brown"/>
+    <n v="7"/>
+    <n v="350"/>
+    <n v="2450"/>
+  </r>
+  <r>
+    <n v="1048"/>
+    <s v="2025-04-02"/>
+    <x v="2"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Smith"/>
+    <n v="3"/>
+    <n v="200"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1049"/>
+    <s v="2025-01-26"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Gonzalez"/>
+    <n v="1"/>
+    <n v="300"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <n v="1050"/>
+    <s v="2025-02-13"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Moore"/>
+    <n v="8"/>
+    <n v="300"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <n v="1051"/>
+    <s v="2025-03-30"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Gonzalez"/>
+    <n v="6"/>
+    <n v="600"/>
+    <n v="3600"/>
+  </r>
+  <r>
+    <n v="1052"/>
+    <s v="2025-02-06"/>
+    <x v="3"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Miller"/>
+    <n v="8"/>
+    <n v="600"/>
+    <n v="4800"/>
+  </r>
+  <r>
+    <n v="1053"/>
+    <s v="2025-03-13"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Johnson"/>
+    <n v="2"/>
+    <n v="120"/>
+    <n v="240"/>
+  </r>
+  <r>
+    <n v="1054"/>
+    <s v="2025-01-19"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Davis"/>
+    <n v="2"/>
+    <n v="900"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <n v="1055"/>
+    <s v="2025-01-29"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Jackson"/>
+    <n v="6"/>
+    <n v="300"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <n v="1056"/>
+    <s v="2025-01-04"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Rodriguez"/>
+    <n v="6"/>
+    <n v="120"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <n v="1057"/>
+    <s v="2025-01-26"/>
+    <x v="1"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Wilson"/>
+    <n v="7"/>
+    <n v="600"/>
+    <n v="4200"/>
+  </r>
+  <r>
+    <n v="1058"/>
+    <s v="2025-04-25"/>
+    <x v="3"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Miller"/>
+    <n v="7"/>
+    <n v="400"/>
+    <n v="2800"/>
+  </r>
+  <r>
+    <n v="1059"/>
+    <s v="2025-04-23"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Wilson"/>
+    <n v="3"/>
+    <n v="350"/>
+    <n v="1050"/>
+  </r>
+  <r>
+    <n v="1060"/>
+    <s v="2025-03-08"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Johnson"/>
+    <n v="4"/>
+    <n v="600"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <n v="1061"/>
+    <s v="2025-01-08"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Smith"/>
+    <n v="8"/>
+    <n v="120"/>
+    <n v="960"/>
+  </r>
+  <r>
+    <n v="1062"/>
+    <s v="2025-04-16"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Gonzalez"/>
+    <n v="2"/>
+    <n v="300"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1063"/>
+    <s v="2025-03-21"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Rodriguez"/>
+    <n v="3"/>
+    <n v="350"/>
+    <n v="1050"/>
+  </r>
+  <r>
+    <n v="1064"/>
+    <s v="2025-04-07"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Martinez"/>
+    <n v="2"/>
+    <n v="250"/>
+    <n v="500"/>
+  </r>
+  <r>
+    <n v="1065"/>
+    <s v="2025-01-14"/>
+    <x v="0"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Martinez"/>
+    <n v="8"/>
+    <n v="400"/>
+    <n v="3200"/>
+  </r>
+  <r>
+    <n v="1066"/>
+    <s v="2025-01-02"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Hernandez"/>
+    <n v="4"/>
+    <n v="300"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1067"/>
+    <s v="2025-03-04"/>
+    <x v="3"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Hernandez"/>
+    <n v="8"/>
+    <n v="400"/>
+    <n v="3200"/>
+  </r>
+  <r>
+    <n v="1068"/>
+    <s v="2025-04-14"/>
+    <x v="3"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Hernandez"/>
+    <n v="4"/>
+    <n v="400"/>
+    <n v="1600"/>
+  </r>
+  <r>
+    <n v="1069"/>
+    <s v="2025-03-15"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Martin"/>
+    <n v="1"/>
+    <n v="300"/>
+    <n v="300"/>
+  </r>
+  <r>
+    <n v="1070"/>
+    <s v="2025-03-30"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Lopez"/>
+    <n v="1"/>
+    <n v="250"/>
+    <n v="250"/>
+  </r>
+  <r>
+    <n v="1071"/>
+    <s v="2025-02-09"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Martinez"/>
+    <n v="3"/>
+    <n v="300"/>
+    <n v="900"/>
+  </r>
+  <r>
+    <n v="1072"/>
+    <s v="2025-04-27"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Hernandez"/>
+    <n v="2"/>
+    <n v="120"/>
+    <n v="240"/>
+  </r>
+  <r>
+    <n v="1073"/>
+    <s v="2025-02-02"/>
+    <x v="1"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Martinez"/>
+    <n v="4"/>
+    <n v="600"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <n v="1074"/>
+    <s v="2025-03-09"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Jackson"/>
+    <n v="8"/>
+    <n v="200"/>
+    <n v="1600"/>
+  </r>
+  <r>
+    <n v="1075"/>
+    <s v="2025-01-08"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Miller"/>
+    <n v="5"/>
+    <n v="250"/>
+    <n v="1250"/>
+  </r>
+  <r>
+    <n v="1076"/>
+    <s v="2025-02-22"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Smith"/>
+    <n v="3"/>
+    <n v="900"/>
+    <n v="2700"/>
+  </r>
+  <r>
+    <n v="1077"/>
+    <s v="2025-03-10"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Johnson"/>
+    <n v="8"/>
+    <n v="120"/>
+    <n v="960"/>
+  </r>
+  <r>
+    <n v="1078"/>
+    <s v="2025-02-15"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Lopez"/>
+    <n v="8"/>
+    <n v="350"/>
+    <n v="2800"/>
+  </r>
+  <r>
+    <n v="1079"/>
+    <s v="2025-01-16"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Martinez"/>
+    <n v="3"/>
+    <n v="350"/>
+    <n v="1050"/>
+  </r>
+  <r>
+    <n v="1080"/>
+    <s v="2025-02-24"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Taylor"/>
+    <n v="2"/>
+    <n v="900"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <n v="1081"/>
+    <s v="2025-01-16"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Garcia"/>
+    <n v="6"/>
+    <n v="120"/>
+    <n v="720"/>
+  </r>
+  <r>
+    <n v="1082"/>
+    <s v="2025-03-07"/>
+    <x v="2"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Miller"/>
+    <n v="8"/>
+    <n v="400"/>
+    <n v="3200"/>
+  </r>
+  <r>
+    <n v="1083"/>
+    <s v="2025-03-18"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Martinez"/>
+    <n v="4"/>
+    <n v="300"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1084"/>
+    <s v="2025-02-04"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Brown"/>
+    <n v="4"/>
+    <n v="250"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <n v="1085"/>
+    <s v="2025-01-11"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Jackson"/>
+    <n v="6"/>
+    <n v="200"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1086"/>
+    <s v="2025-03-14"/>
+    <x v="0"/>
+    <x v="7"/>
+    <s v="Technology"/>
+    <s v="Wilson"/>
+    <n v="3"/>
+    <n v="400"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1087"/>
+    <s v="2025-04-26"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Garcia"/>
+    <n v="3"/>
+    <n v="350"/>
+    <n v="1050"/>
+  </r>
+  <r>
+    <n v="1088"/>
+    <s v="2025-02-02"/>
+    <x v="2"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Gonzalez"/>
+    <n v="8"/>
+    <n v="350"/>
+    <n v="2800"/>
+  </r>
+  <r>
+    <n v="1089"/>
+    <s v="2025-02-02"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Thomas"/>
+    <n v="1"/>
+    <n v="120"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <n v="1090"/>
+    <s v="2025-02-28"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Miller"/>
+    <n v="1"/>
+    <n v="120"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <n v="1091"/>
+    <s v="2025-01-03"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Lopez"/>
+    <n v="1"/>
+    <n v="250"/>
+    <n v="250"/>
+  </r>
+  <r>
+    <n v="1092"/>
+    <s v="2025-01-19"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Brown"/>
+    <n v="5"/>
+    <n v="600"/>
+    <n v="3000"/>
+  </r>
+  <r>
+    <n v="1093"/>
+    <s v="2025-01-28"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Anderson"/>
+    <n v="8"/>
+    <n v="200"/>
+    <n v="1600"/>
+  </r>
+  <r>
+    <n v="1094"/>
+    <s v="2025-04-22"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Miller"/>
+    <n v="3"/>
+    <n v="900"/>
+    <n v="2700"/>
+  </r>
+  <r>
+    <n v="1095"/>
+    <s v="2025-03-04"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Jones"/>
+    <n v="7"/>
+    <n v="350"/>
+    <n v="2450"/>
+  </r>
+  <r>
+    <n v="1096"/>
+    <s v="2025-01-28"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Jones"/>
+    <n v="3"/>
+    <n v="200"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1097"/>
+    <s v="2025-03-08"/>
+    <x v="3"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Williams"/>
+    <n v="4"/>
+    <n v="120"/>
+    <n v="480"/>
+  </r>
+  <r>
+    <n v="1098"/>
+    <s v="2025-03-27"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Martin"/>
+    <n v="3"/>
+    <n v="900"/>
+    <n v="2700"/>
+  </r>
+  <r>
+    <n v="1099"/>
+    <s v="2025-01-09"/>
+    <x v="2"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Miller"/>
+    <n v="2"/>
+    <n v="900"/>
+    <n v="1800"/>
+  </r>
+  <r>
+    <n v="1100"/>
+    <s v="2025-04-04"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Davis"/>
+    <n v="8"/>
+    <n v="120"/>
+    <n v="960"/>
+  </r>
+  <r>
+    <n v="1101"/>
+    <s v="2025-01-13"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Gonzalez"/>
+    <n v="5"/>
+    <n v="200"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <n v="1102"/>
+    <s v="2025-03-21"/>
+    <x v="3"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Smith"/>
+    <n v="3"/>
+    <n v="200"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1103"/>
+    <s v="2025-01-18"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Wilson"/>
+    <n v="8"/>
+    <n v="300"/>
+    <n v="2400"/>
+  </r>
+  <r>
+    <n v="1104"/>
+    <s v="2025-01-16"/>
+    <x v="1"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Davis"/>
+    <n v="8"/>
+    <n v="900"/>
+    <n v="7200"/>
+  </r>
+  <r>
+    <n v="1105"/>
+    <s v="2025-02-25"/>
+    <x v="3"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Johnson"/>
+    <n v="4"/>
+    <n v="300"/>
+    <n v="1200"/>
+  </r>
+  <r>
+    <n v="1106"/>
+    <s v="2025-01-04"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="Technology"/>
+    <s v="Jackson"/>
+    <n v="4"/>
+    <n v="900"/>
+    <n v="3600"/>
+  </r>
+  <r>
+    <n v="1107"/>
+    <s v="2025-01-24"/>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Thomas"/>
+    <n v="4"/>
+    <n v="250"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <n v="1108"/>
+    <s v="2025-03-28"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Taylor"/>
+    <n v="8"/>
+    <n v="600"/>
+    <n v="4800"/>
+  </r>
+  <r>
+    <n v="1109"/>
+    <s v="2025-01-06"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Lopez"/>
+    <n v="7"/>
+    <n v="350"/>
+    <n v="2450"/>
+  </r>
+  <r>
+    <n v="1110"/>
+    <s v="2025-02-26"/>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="Furniture"/>
+    <s v="Jones"/>
+    <n v="5"/>
+    <n v="200"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <n v="1111"/>
+    <s v="2025-02-27"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Jackson"/>
+    <n v="7"/>
+    <n v="300"/>
+    <n v="2100"/>
+  </r>
+  <r>
+    <n v="1112"/>
+    <s v="2025-02-08"/>
+    <x v="3"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Martin"/>
+    <n v="8"/>
+    <n v="250"/>
+    <n v="2000"/>
+  </r>
+  <r>
+    <n v="1113"/>
+    <s v="2025-01-13"/>
+    <x v="3"/>
+    <x v="6"/>
+    <s v="Technology"/>
+    <s v="Gonzalez"/>
+    <n v="8"/>
+    <n v="600"/>
+    <n v="4800"/>
+  </r>
+  <r>
+    <n v="1114"/>
+    <s v="2025-03-08"/>
+    <x v="2"/>
+    <x v="1"/>
+    <s v="Technology"/>
+    <s v="Davis"/>
+    <n v="2"/>
+    <n v="300"/>
+    <n v="600"/>
+  </r>
+  <r>
+    <n v="1115"/>
+    <s v="2025-04-26"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Furniture"/>
+    <s v="Moore"/>
+    <n v="2"/>
+    <n v="120"/>
+    <n v="240"/>
+  </r>
+  <r>
+    <n v="1116"/>
+    <s v="2025-04-19"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Garcia"/>
+    <n v="8"/>
+    <n v="250"/>
+    <n v="2000"/>
+  </r>
+  <r>
+    <n v="1117"/>
+    <s v="2025-01-04"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Thomas"/>
+    <n v="4"/>
+    <n v="350"/>
+    <n v="1400"/>
+  </r>
+  <r>
+    <n v="1118"/>
+    <s v="2025-04-04"/>
+    <x v="2"/>
+    <x v="3"/>
+    <s v="Technology"/>
+    <s v="Garcia"/>
+    <n v="4"/>
+    <n v="250"/>
+    <n v="1000"/>
+  </r>
+  <r>
+    <n v="1119"/>
+    <s v="2025-02-01"/>
+    <x v="3"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Martinez"/>
+    <n v="7"/>
+    <n v="350"/>
+    <n v="2450"/>
+  </r>
+  <r>
+    <n v="1120"/>
+    <s v="2025-03-13"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="Furniture"/>
+    <s v="Davis"/>
+    <n v="1"/>
+    <n v="350"/>
+    <n v="350"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4780CDE4-C79D-4ADC-BA3B-54EC04419CAB}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K8:L10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="2"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="6"/>
+        <item h="1" x="3"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6635B3F2-4F44-4EF3-8A53-BD50ECFF75F7}" name="PivotTable2" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K1:L6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -729,10 +2264,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="11" max="11" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="16.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -760,8 +2299,14 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -789,8 +2334,14 @@
       <c r="I2">
         <v>1800</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="3">
+        <v>49560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -818,8 +2369,14 @@
       <c r="I3">
         <v>2400</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="3">
+        <v>56690</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -847,8 +2404,14 @@
       <c r="I4">
         <v>2100</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="3">
+        <v>55200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -876,8 +2439,14 @@
       <c r="I5">
         <v>700</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="3">
+        <v>59610</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -905,8 +2474,14 @@
       <c r="I6">
         <v>1250</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L6" s="3">
+        <v>221060</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1006</v>
       </c>
@@ -935,7 +2510,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1007</v>
       </c>
@@ -963,8 +2538,14 @@
       <c r="I8">
         <v>1400</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1008</v>
       </c>
@@ -992,8 +2573,14 @@
       <c r="I9">
         <v>1000</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="3">
+        <v>61200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1009</v>
       </c>
@@ -1021,8 +2608,14 @@
       <c r="I10">
         <v>600</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L10" s="3">
+        <v>61200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1010</v>
       </c>
@@ -1051,7 +2644,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1011</v>
       </c>
@@ -1079,8 +2672,12 @@
       <c r="I12">
         <v>900</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="K12" t="e" cm="1">
+        <f t="array" aca="1" ref="K12" ca="1">K11()</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1012</v>
       </c>
@@ -1109,7 +2706,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1013</v>
       </c>
@@ -1138,7 +2735,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1014</v>
       </c>
@@ -1167,7 +2764,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1015</v>
       </c>
@@ -4239,6 +5836,12 @@
       </c>
       <c r="I121">
         <v>350</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I122">
+        <f>SUM(I2:I121)</f>
+        <v>221060</v>
       </c>
     </row>
   </sheetData>
